--- a/sample_data/명세서_외화자산부채명세서.xlsx
+++ b/sample_data/명세서_외화자산부채명세서.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -995,6 +995,427 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TXN009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Highland Textiles Ltd</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>108 외상매출금(외화)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1892.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>15139200</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1885.6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>7542400</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>분할결제 1차</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TXN009</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Highland Textiles Ltd</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>108 외상매출금(외화)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1892.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>15139200</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1901.3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7605200</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>분할결제 2차</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TXN010</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kowloon Freight Co</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>채무</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>251 외상매입금(외화)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>200000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>36980000</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>200000</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>기말 현재 미결제</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TXN011</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Alpine Precision AG</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>108 외상매출금(외화)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1620.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>9723000</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1750</v>
+      </c>
+      <c r="M13" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>기중 결제 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TXN012</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Maple Ridge Supplies</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>채무</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>251 외상매입금(외화)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1015.8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>15237000</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1008.4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>15126000</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>기중 결제 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TXN013</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Outback Mining Corp</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>108 외상매출금(외화)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>915.6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>22890000</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>980</v>
+      </c>
+      <c r="M15" t="n">
+        <v>24500000</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>기중 결제 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TXN014</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Marina Bay Logistics</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>채무</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>251 외상매입금(외화)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1078.3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>12939600</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>12000</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>기말 현재 미결제</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
